--- a/zayavki/2026-10-29_Заявка_2.xlsx
+++ b/zayavki/2026-10-29_Заявка_2.xlsx
@@ -527,11 +527,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9955</v>
+        <v>10951</v>
       </c>
       <c r="F4" s="4" t="n">
         <f aca="false">C4*E4</f>
-        <v>238920</v>
+        <v>262824</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -548,11 +548,11 @@
         <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1110</v>
+        <v>1221</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">C5*E5</f>
-        <v>39960</v>
+        <v>43956</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -569,11 +569,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2629</v>
+        <v>2892</v>
       </c>
       <c r="F6" s="4" t="n">
         <f aca="false">C6*E6</f>
-        <v>63096</v>
+        <v>69408</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -590,11 +590,11 @@
         <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1517</v>
+        <v>1668</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">C7*E7</f>
-        <v>18204</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -603,7 +603,7 @@
       </c>
       <c r="F8" s="6" t="n">
         <f aca="false">F4+F5+F6+F7</f>
-        <v>360180</v>
+        <v>396204</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
